--- a/results/Int All Data -0.1/Linea_fi_explain.xlsx
+++ b/results/Int All Data -0.1/Linea_fi_explain.xlsx
@@ -1697,7 +1697,7 @@
         <v>0.01968771003889334</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009594501912005017</v>
+        <v>0.009591084277008433</v>
       </c>
       <c r="J3" t="n">
         <v>0.003509408983485287</v>
@@ -1736,7 +1736,7 @@
         <v>0.003207400077936771</v>
       </c>
       <c r="V3" t="n">
-        <v>0.009591084277008433</v>
+        <v>0.009594501912005017</v>
       </c>
       <c r="W3" t="n">
         <v>0.003226826699732362</v>
@@ -1898,7 +1898,7 @@
         <v>-0.0001401464610944847</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.001718703598893365</v>
+        <v>0.001711787969571097</v>
       </c>
       <c r="BY3" t="n">
         <v>0.0008942409353646597</v>
@@ -1913,7 +1913,7 @@
         <v>0.0004897867829015589</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.01180204281134374</v>
+        <v>0.01180548871072348</v>
       </c>
       <c r="CD3" t="n">
         <v>0.000893920038447392</v>
@@ -1922,7 +1922,7 @@
         <v>-0.0005921875441414891</v>
       </c>
       <c r="CF3" t="n">
-        <v>-1.064785888785556e-05</v>
+        <v>-7.633540030756993e-06</v>
       </c>
       <c r="CG3" t="n">
         <v>0.4162160032064128</v>
@@ -1934,7 +1934,7 @@
         <v>0.2610038260342625</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0.0001435640960910667</v>
+        <v>-0.0001401464610944847</v>
       </c>
       <c r="CK3" t="n">
         <v>0.001427106853169375</v>
@@ -1964,7 +1964,7 @@
         <v>0.3551463340323712</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.09507062070809273</v>
+        <v>0.09506713030669658</v>
       </c>
       <c r="CU3" t="n">
         <v>0.1171465157331134</v>
@@ -2093,7 +2093,7 @@
         <v>-0.002140994749690252</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.009362756510351278</v>
+        <v>0.009359406426599184</v>
       </c>
       <c r="EL3" t="n">
         <v>0.0005111787991347617</v>
@@ -2166,7 +2166,7 @@
         <v>0.01532420321718317</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01084908421025536</v>
+        <v>0.01084747139040763</v>
       </c>
       <c r="J4" t="n">
         <v>0.006117761102911182</v>
@@ -2205,7 +2205,7 @@
         <v>0.01019422671692311</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01084747139040763</v>
+        <v>0.01084908421025536</v>
       </c>
       <c r="W4" t="n">
         <v>0.005435746409787382</v>
@@ -2367,7 +2367,7 @@
         <v>0.0005577182261625328</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.006450841365073076</v>
+        <v>0.00643453507860145</v>
       </c>
       <c r="BY4" t="n">
         <v>0.004941523202425512</v>
@@ -2382,7 +2382,7 @@
         <v>0.01007633380307262</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.01840831100250933</v>
+        <v>0.01841180076720806</v>
       </c>
       <c r="CD4" t="n">
         <v>0.01004895250016173</v>
@@ -2391,7 +2391,7 @@
         <v>0.002702208311420976</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.0007389066859100744</v>
+        <v>0.0007315309097272466</v>
       </c>
       <c r="CG4" t="n">
         <v>0.1286835425301166</v>
@@ -2403,7 +2403,7 @@
         <v>0.05934315759154355</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0005561684669203346</v>
+        <v>0.0005577182261625328</v>
       </c>
       <c r="CK4" t="n">
         <v>0.006246708660931896</v>
@@ -2433,7 +2433,7 @@
         <v>0.1405563167471571</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.08803794839937493</v>
+        <v>0.0880395708768941</v>
       </c>
       <c r="CU4" t="n">
         <v>0.03241683468493861</v>
@@ -2562,7 +2562,7 @@
         <v>0.01506777276759831</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.03421293834176262</v>
+        <v>0.03421440327459885</v>
       </c>
       <c r="EL4" t="n">
         <v>0.000957327266059396</v>
@@ -3329,7 +3329,7 @@
         <v>-0.002682087433830829</v>
       </c>
       <c r="CF6" t="n">
-        <v>-1.797724776739784e-05</v>
+        <v>-1.740884627655093e-05</v>
       </c>
       <c r="CG6" t="n">
         <v>0.2997109401505901</v>
@@ -3500,7 +3500,7 @@
         <v>-0.003038098442000753</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.004133808739409333</v>
+        <v>-0.004142183948789568</v>
       </c>
       <c r="EL6" t="n">
         <v>-2.413904087544827e-05</v>
@@ -3798,7 +3798,7 @@
         <v>8.506754348939214e-05</v>
       </c>
       <c r="CF7" t="n">
-        <v>5.078654387852821e-05</v>
+        <v>9.929948179366876e-05</v>
       </c>
       <c r="CG7" t="n">
         <v>0.4388031190089323</v>
@@ -3840,7 +3840,7 @@
         <v>0.3853846682341849</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.06551492017641142</v>
+        <v>0.06549746816943061</v>
       </c>
       <c r="CU7" t="n">
         <v>0.1155750135403502</v>
@@ -4042,7 +4042,7 @@
         <v>0.03444575770599838</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01310141063744527</v>
+        <v>0.01307577837497089</v>
       </c>
       <c r="J8" t="n">
         <v>0.005245219784348995</v>
@@ -4081,7 +4081,7 @@
         <v>0.005133827953028655</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01307577837497089</v>
+        <v>0.01310141063744527</v>
       </c>
       <c r="W8" t="n">
         <v>0.006697366359023816</v>
@@ -4258,7 +4258,7 @@
         <v>0.0006866356496140202</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.02299699149194956</v>
+        <v>0.0230228357372976</v>
       </c>
       <c r="CD8" t="n">
         <v>0.00426002254662246</v>
@@ -4279,7 +4279,7 @@
         <v>0.3000353958262681</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.0001732839403421532</v>
+        <v>0.0001818280278336082</v>
       </c>
       <c r="CK8" t="n">
         <v>0.00493067271860492</v>
@@ -4712,7 +4712,7 @@
         <v>0.0006040268456375397</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.01542185338865842</v>
+        <v>0.01535269709543574</v>
       </c>
       <c r="BY9" t="n">
         <v>0.005995864920744287</v>
@@ -4736,7 +4736,7 @@
         <v>0.002949340735600292</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0008644536652835377</v>
+        <v>0.0007952973720608547</v>
       </c>
       <c r="CG9" t="n">
         <v>0.5881638320027769</v>
